--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-10-2025.xlsx
@@ -589,29 +589,29 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -710,29 +710,29 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -831,29 +831,29 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -952,29 +952,29 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -1073,29 +1073,29 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -1194,29 +1194,29 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -1315,29 +1315,29 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -1436,29 +1436,29 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -1557,29 +1557,29 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -1678,29 +1678,29 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -1799,29 +1799,29 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -1920,29 +1920,29 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -2041,29 +2041,29 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -2162,29 +2162,29 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -2283,29 +2283,29 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -2501,29 +2501,29 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -2622,29 +2622,29 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -2743,29 +2743,29 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -2864,29 +2864,29 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -2985,29 +2985,29 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -3106,29 +3106,29 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -3227,29 +3227,29 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -3348,29 +3348,29 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
@@ -3469,29 +3469,29 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6f376e8e5+80021]
-	GetHandleVerifier [0x0x7ff6f376e940+80112]
-	(No symbol) [0x0x7ff6f34f060f]
-	(No symbol) [0x0x7ff6f3548854]
-	(No symbol) [0x0x7ff6f3548b1c]
-	(No symbol) [0x0x7ff6f359c927]
-	(No symbol) [0x0x7ff6f357126f]
-	(No symbol) [0x0x7ff6f359968a]
-	(No symbol) [0x0x7ff6f3571003]
-	(No symbol) [0x0x7ff6f35395d1]
-	(No symbol) [0x0x7ff6f353a3f3]
-	GetHandleVerifier [0x0x7ff6f3a2dc7d+2960429]
-	GetHandleVerifier [0x0x7ff6f3a27f3a+2936554]
-	GetHandleVerifier [0x0x7ff6f3a48977+3070247]
-	GetHandleVerifier [0x0x7ff6f37883ce+185214]
-	GetHandleVerifier [0x0x7ff6f378fe1f+216527]
-	GetHandleVerifier [0x0x7ff6f3777b24+117460]
-	GetHandleVerifier [0x0x7ff6f3777cdf+117903]
-	GetHandleVerifier [0x0x7ff6f375dbb8+11112]
-	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
-	RtlUserThreadStart [0x0x7ffc62fac53c+44]
+	GetHandleVerifier [0x0x7ff65835e8e5+80021]
+	GetHandleVerifier [0x0x7ff65835e940+80112]
+	(No symbol) [0x0x7ff6580e060f]
+	(No symbol) [0x0x7ff658138854]
+	(No symbol) [0x0x7ff658138b1c]
+	(No symbol) [0x0x7ff65818c927]
+	(No symbol) [0x0x7ff65816126f]
+	(No symbol) [0x0x7ff65818968a]
+	(No symbol) [0x0x7ff658161003]
+	(No symbol) [0x0x7ff6581295d1]
+	(No symbol) [0x0x7ff65812a3f3]
+	GetHandleVerifier [0x0x7ff65861dc7d+2960429]
+	GetHandleVerifier [0x0x7ff658617f3a+2936554]
+	GetHandleVerifier [0x0x7ff658638977+3070247]
+	GetHandleVerifier [0x0x7ff6583783ce+185214]
+	GetHandleVerifier [0x0x7ff65837fe1f+216527]
+	GetHandleVerifier [0x0x7ff658367b24+117460]
+	GetHandleVerifier [0x0x7ff658367cdf+117903]
+	GetHandleVerifier [0x0x7ff65834dbb8+11112]
+	BaseThreadInitThunk [0x0x7ffe5070e8d7+23]
+	RtlUserThreadStart [0x0x7ffe50e4c53c+44]
 </t>
         </is>
       </c>
